--- a/CR_Delta_Report.xlsx
+++ b/CR_Delta_Report.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-15 07:59:04</t>
+          <t>2026-03-13 21:49:08</t>
         </is>
       </c>
     </row>
